--- a/data/nzd0507/nzd0507.xlsx
+++ b/data/nzd0507/nzd0507.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I327"/>
+  <dimension ref="A1:I328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11223,7 +11223,7 @@
         <v>348.61</v>
       </c>
       <c r="G327" t="n">
-        <v>343.05</v>
+        <v>339.71</v>
       </c>
       <c r="H327" t="n">
         <v>350</v>
@@ -11231,6 +11231,39 @@
       <c r="I327" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>324.01</v>
+      </c>
+      <c r="C328" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="D328" t="n">
+        <v>321.98</v>
+      </c>
+      <c r="E328" t="n">
+        <v>349.49</v>
+      </c>
+      <c r="F328" t="n">
+        <v>336.87</v>
+      </c>
+      <c r="G328" t="n">
+        <v>328.59</v>
+      </c>
+      <c r="H328" t="n">
+        <v>339.65</v>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B345"/>
+  <dimension ref="A1:B346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14698,6 +14731,16 @@
       </c>
       <c r="B345" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -14866,28 +14909,28 @@
         <v>0.082</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02445906326915314</v>
+        <v>-0.0295387383367822</v>
       </c>
       <c r="J2" t="n">
+        <v>327</v>
+      </c>
+      <c r="K2" t="n">
         <v>326</v>
       </c>
-      <c r="K2" t="n">
-        <v>325</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0005528965244100403</v>
+        <v>0.0008080881847337684</v>
       </c>
       <c r="M2" t="n">
-        <v>5.85032734765124</v>
+        <v>5.859017892107141</v>
       </c>
       <c r="N2" t="n">
-        <v>55.04762051260596</v>
+        <v>55.09050685850331</v>
       </c>
       <c r="O2" t="n">
-        <v>7.419408366750408</v>
+        <v>7.422297949995224</v>
       </c>
       <c r="P2" t="n">
-        <v>333.0112596462837</v>
+        <v>333.0690422659053</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -14948,28 +14991,28 @@
         <v>0.0743</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04342182359850586</v>
+        <v>-0.05021719624216369</v>
       </c>
       <c r="J3" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K3" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001633814995903426</v>
+        <v>0.002183268914499048</v>
       </c>
       <c r="M3" t="n">
-        <v>6.272621579526803</v>
+        <v>6.28778270005235</v>
       </c>
       <c r="N3" t="n">
-        <v>59.41298790693812</v>
+        <v>59.61754715193256</v>
       </c>
       <c r="O3" t="n">
-        <v>7.707982090465579</v>
+        <v>7.721240000928125</v>
       </c>
       <c r="P3" t="n">
-        <v>334.1431574467077</v>
+        <v>334.2198401819421</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15030,28 +15073,28 @@
         <v>0.0709</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.003313202810021373</v>
+        <v>-0.009464998714357178</v>
       </c>
       <c r="J4" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L4" t="n">
-        <v>7.675347312496861e-06</v>
+        <v>6.275248526377286e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.866835586461695</v>
+        <v>6.87662157006905</v>
       </c>
       <c r="N4" t="n">
-        <v>73.75185761299578</v>
+        <v>73.84286956189804</v>
       </c>
       <c r="O4" t="n">
-        <v>8.587890172387848</v>
+        <v>8.593187392457937</v>
       </c>
       <c r="P4" t="n">
-        <v>332.2891268378906</v>
+        <v>332.3585470980125</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15108,28 +15151,28 @@
         <v>0.0713</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0610315970721877</v>
+        <v>-0.05876295784385695</v>
       </c>
       <c r="J5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004602032399353861</v>
+        <v>0.004289534411133888</v>
       </c>
       <c r="M5" t="n">
-        <v>5.220169824585659</v>
+        <v>5.216230874087006</v>
       </c>
       <c r="N5" t="n">
-        <v>41.54653780857448</v>
+        <v>41.46253417992634</v>
       </c>
       <c r="O5" t="n">
-        <v>6.445660385761452</v>
+        <v>6.439140795162531</v>
       </c>
       <c r="P5" t="n">
-        <v>347.3441592221331</v>
+        <v>347.318558645033</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15186,28 +15229,28 @@
         <v>0.055</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04330724856226604</v>
+        <v>-0.04724846864220775</v>
       </c>
       <c r="J6" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K6" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001980060951476292</v>
+        <v>0.002364196824310882</v>
       </c>
       <c r="M6" t="n">
-        <v>5.270062695776721</v>
+        <v>5.270885187886116</v>
       </c>
       <c r="N6" t="n">
-        <v>48.74837411134851</v>
+        <v>48.72922479572215</v>
       </c>
       <c r="O6" t="n">
-        <v>6.982003588608968</v>
+        <v>6.980632120067792</v>
       </c>
       <c r="P6" t="n">
-        <v>344.571291004497</v>
+        <v>344.6157659070136</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15264,28 +15307,28 @@
         <v>0.0525</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2622906974425649</v>
+        <v>-0.2694208242440529</v>
       </c>
       <c r="J7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05497345185232527</v>
+        <v>0.0580378514540858</v>
       </c>
       <c r="M7" t="n">
-        <v>5.99111856336019</v>
+        <v>5.986873980389965</v>
       </c>
       <c r="N7" t="n">
-        <v>60.98669078629375</v>
+        <v>60.94107021373694</v>
       </c>
       <c r="O7" t="n">
-        <v>7.809397594327859</v>
+        <v>7.806476171342415</v>
       </c>
       <c r="P7" t="n">
-        <v>344.1804519941761</v>
+        <v>344.2605389578691</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15342,28 +15385,28 @@
         <v>0.0557</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2865895190422484</v>
+        <v>-0.288644936224159</v>
       </c>
       <c r="J8" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K8" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08003550467751341</v>
+        <v>0.08150031943241154</v>
       </c>
       <c r="M8" t="n">
-        <v>5.241317406675744</v>
+        <v>5.235388206894402</v>
       </c>
       <c r="N8" t="n">
-        <v>48.68411477184487</v>
+        <v>48.57057171279142</v>
       </c>
       <c r="O8" t="n">
-        <v>6.977400287488519</v>
+        <v>6.969259050486746</v>
       </c>
       <c r="P8" t="n">
-        <v>350.6762603285861</v>
+        <v>350.6994547904386</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -15405,7 +15448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I327"/>
+  <dimension ref="A1:I328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30759,7 +30802,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>-45.86511129045746,170.7424342974638</t>
+          <t>-45.865125550085,170.74239643486868</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -30770,6 +30813,53 @@
       <c r="I327" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-45.86217828827393,170.74094399768484</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-45.86279888403424,170.74105648032875</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-45.863419356303176,170.7412029367106</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-45.863977568856285,170.741727618369</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-45.86458012903506,170.74195564124025</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-45.865173025158775,170.7422703772292</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-45.86565626768742,170.7428715338905</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0507/nzd0507.xlsx
+++ b/data/nzd0507/nzd0507.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I328"/>
+  <dimension ref="A1:I329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11264,6 +11264,39 @@
       <c r="I328" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>333.01</v>
+      </c>
+      <c r="C329" t="n">
+        <v>331.81</v>
+      </c>
+      <c r="D329" t="n">
+        <v>328.93</v>
+      </c>
+      <c r="E329" t="n">
+        <v>347.31</v>
+      </c>
+      <c r="F329" t="n">
+        <v>333.6</v>
+      </c>
+      <c r="G329" t="n">
+        <v>327.9</v>
+      </c>
+      <c r="H329" t="n">
+        <v>340.29</v>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B346"/>
+  <dimension ref="A1:B347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14741,6 +14774,16 @@
       </c>
       <c r="B346" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -14909,28 +14952,28 @@
         <v>0.082</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0295387383367822</v>
+        <v>-0.02909715866709761</v>
       </c>
       <c r="J2" t="n">
+        <v>328</v>
+      </c>
+      <c r="K2" t="n">
         <v>327</v>
       </c>
-      <c r="K2" t="n">
-        <v>326</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0008080881847337684</v>
+        <v>0.0007889402815421942</v>
       </c>
       <c r="M2" t="n">
-        <v>5.859017892107141</v>
+        <v>5.843224797751118</v>
       </c>
       <c r="N2" t="n">
-        <v>55.09050685850331</v>
+        <v>54.92365237505186</v>
       </c>
       <c r="O2" t="n">
-        <v>7.422297949995224</v>
+        <v>7.411049343719947</v>
       </c>
       <c r="P2" t="n">
-        <v>333.0690422659053</v>
+        <v>333.0640143808293</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -14991,28 +15034,28 @@
         <v>0.0743</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05021719624216369</v>
+        <v>-0.05085708654351377</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002183268914499048</v>
+        <v>0.002252713701533904</v>
       </c>
       <c r="M3" t="n">
-        <v>6.28778270005235</v>
+        <v>6.271829975411698</v>
       </c>
       <c r="N3" t="n">
-        <v>59.61754715193256</v>
+        <v>59.43924932231434</v>
       </c>
       <c r="O3" t="n">
-        <v>7.721240000928125</v>
+        <v>7.709685423045116</v>
       </c>
       <c r="P3" t="n">
-        <v>334.2198401819421</v>
+        <v>334.2270680371431</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15073,28 +15116,28 @@
         <v>0.0709</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.009464998714357178</v>
+        <v>-0.011363803353527</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L4" t="n">
-        <v>6.275248526377286e-05</v>
+        <v>9.097066973806633e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.87662157006905</v>
+        <v>6.865333746908721</v>
       </c>
       <c r="N4" t="n">
-        <v>73.84286956189804</v>
+        <v>73.64823185871596</v>
       </c>
       <c r="O4" t="n">
-        <v>8.593187392457937</v>
+        <v>8.581854802938347</v>
       </c>
       <c r="P4" t="n">
-        <v>332.3585470980125</v>
+        <v>332.3799949695585</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15151,28 +15194,28 @@
         <v>0.0713</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05876295784385695</v>
+        <v>-0.05783699062658833</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004289534411133888</v>
+        <v>0.004180630831628784</v>
       </c>
       <c r="M5" t="n">
-        <v>5.216230874087006</v>
+        <v>5.20521018143144</v>
       </c>
       <c r="N5" t="n">
-        <v>41.46253417992634</v>
+        <v>41.34337556332977</v>
       </c>
       <c r="O5" t="n">
-        <v>6.439140795162531</v>
+        <v>6.429881457953153</v>
       </c>
       <c r="P5" t="n">
-        <v>347.318558645033</v>
+        <v>347.308099419517</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15229,28 +15272,28 @@
         <v>0.055</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04724846864220775</v>
+        <v>-0.05308387187346887</v>
       </c>
       <c r="J6" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K6" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002364196824310882</v>
+        <v>0.002982999564132394</v>
       </c>
       <c r="M6" t="n">
-        <v>5.270885187886116</v>
+        <v>5.279755941026555</v>
       </c>
       <c r="N6" t="n">
-        <v>48.72922479572215</v>
+        <v>48.86865265478222</v>
       </c>
       <c r="O6" t="n">
-        <v>6.980632120067792</v>
+        <v>6.990611751111788</v>
       </c>
       <c r="P6" t="n">
-        <v>344.6157659070136</v>
+        <v>344.6816794698632</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15307,28 +15350,28 @@
         <v>0.0525</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2694208242440529</v>
+        <v>-0.274918795097123</v>
       </c>
       <c r="J7" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K7" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0580378514540858</v>
+        <v>0.06039518370083719</v>
       </c>
       <c r="M7" t="n">
-        <v>5.986873980389965</v>
+        <v>5.995076306113399</v>
       </c>
       <c r="N7" t="n">
-        <v>60.94107021373694</v>
+        <v>61.01092344842698</v>
       </c>
       <c r="O7" t="n">
-        <v>7.806476171342415</v>
+        <v>7.810948946730287</v>
       </c>
       <c r="P7" t="n">
-        <v>344.2605389578691</v>
+        <v>344.322641066842</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15385,28 +15428,28 @@
         <v>0.0557</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.288644936224159</v>
+        <v>-0.2902829388562159</v>
       </c>
       <c r="J8" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K8" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08150031943241154</v>
+        <v>0.08277935791176616</v>
       </c>
       <c r="M8" t="n">
-        <v>5.235388206894402</v>
+        <v>5.227431817152175</v>
       </c>
       <c r="N8" t="n">
-        <v>48.57057171279142</v>
+        <v>48.44518249007979</v>
       </c>
       <c r="O8" t="n">
-        <v>6.969259050486746</v>
+        <v>6.960257358034959</v>
       </c>
       <c r="P8" t="n">
-        <v>350.6994547904386</v>
+        <v>350.717956783387</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -15448,7 +15491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I328"/>
+  <dimension ref="A1:I329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30863,6 +30906,53 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-45.86216705507616,170.74105877621875</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-45.86278626534937,170.741185416309</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-45.86340942500815,170.7412913025758</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-45.8639833408009,170.74170078724325</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-45.86459250003545,170.7419174331839</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-45.86517597099946,170.74226255530039</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-45.865653318527706,170.74287861302608</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0507/nzd0507.xlsx
+++ b/data/nzd0507/nzd0507.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I329"/>
+  <dimension ref="A1:I333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11297,6 +11297,138 @@
       <c r="I329" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>330.56</v>
+      </c>
+      <c r="C330" t="n">
+        <v>328.71</v>
+      </c>
+      <c r="D330" t="n">
+        <v>328</v>
+      </c>
+      <c r="E330" t="n">
+        <v>346.33</v>
+      </c>
+      <c r="F330" t="n">
+        <v>334.94</v>
+      </c>
+      <c r="G330" t="n">
+        <v>327.25</v>
+      </c>
+      <c r="H330" t="n">
+        <v>340.27</v>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>331.75</v>
+      </c>
+      <c r="C331" t="n">
+        <v>330.21</v>
+      </c>
+      <c r="D331" t="n">
+        <v>332.15</v>
+      </c>
+      <c r="E331" t="n">
+        <v>348.89</v>
+      </c>
+      <c r="F331" t="n">
+        <v>342.6</v>
+      </c>
+      <c r="G331" t="n">
+        <v>336.72</v>
+      </c>
+      <c r="H331" t="n">
+        <v>347.44</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>330.29</v>
+      </c>
+      <c r="C332" t="n">
+        <v>328.37</v>
+      </c>
+      <c r="D332" t="n">
+        <v>328.58</v>
+      </c>
+      <c r="E332" t="n">
+        <v>345.76</v>
+      </c>
+      <c r="F332" t="n">
+        <v>339.67</v>
+      </c>
+      <c r="G332" t="n">
+        <v>333.71</v>
+      </c>
+      <c r="H332" t="n">
+        <v>345.37</v>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>333.38</v>
+      </c>
+      <c r="C333" t="n">
+        <v>332.56</v>
+      </c>
+      <c r="D333" t="n">
+        <v>328.58</v>
+      </c>
+      <c r="E333" t="n">
+        <v>349.67</v>
+      </c>
+      <c r="F333" t="n">
+        <v>343.04</v>
+      </c>
+      <c r="G333" t="n">
+        <v>333.71</v>
+      </c>
+      <c r="H333" t="n">
+        <v>350.22</v>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B347"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14784,6 +14916,46 @@
       </c>
       <c r="B347" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -14952,28 +15124,28 @@
         <v>0.082</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02909715866709761</v>
+        <v>-0.03096177884438537</v>
       </c>
       <c r="J2" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007889402815421942</v>
+        <v>0.0009148597791395208</v>
       </c>
       <c r="M2" t="n">
-        <v>5.843224797751118</v>
+        <v>5.789102900586212</v>
       </c>
       <c r="N2" t="n">
-        <v>54.92365237505186</v>
+        <v>54.28523115537102</v>
       </c>
       <c r="O2" t="n">
-        <v>7.411049343719947</v>
+        <v>7.367851189822648</v>
       </c>
       <c r="P2" t="n">
-        <v>333.0640143808293</v>
+        <v>333.0853332495731</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15034,28 +15206,28 @@
         <v>0.0743</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05085708654351377</v>
+        <v>-0.05762914648932047</v>
       </c>
       <c r="J3" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K3" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002252713701533904</v>
+        <v>0.002955059072883737</v>
       </c>
       <c r="M3" t="n">
-        <v>6.271829975411698</v>
+        <v>6.229548146277886</v>
       </c>
       <c r="N3" t="n">
-        <v>59.43924932231434</v>
+        <v>58.85414167212879</v>
       </c>
       <c r="O3" t="n">
-        <v>7.709685423045116</v>
+        <v>7.671645304113635</v>
       </c>
       <c r="P3" t="n">
-        <v>334.2270680371431</v>
+        <v>334.3039343274995</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15116,28 +15288,28 @@
         <v>0.0709</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.011363803353527</v>
+        <v>-0.0177711643382485</v>
       </c>
       <c r="J4" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K4" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L4" t="n">
-        <v>9.097066973806633e-05</v>
+        <v>0.0002275419185215899</v>
       </c>
       <c r="M4" t="n">
-        <v>6.865333746908721</v>
+        <v>6.81553772365961</v>
       </c>
       <c r="N4" t="n">
-        <v>73.64823185871596</v>
+        <v>72.88121550439151</v>
       </c>
       <c r="O4" t="n">
-        <v>8.581854802938347</v>
+        <v>8.537049578419438</v>
       </c>
       <c r="P4" t="n">
-        <v>332.3799949695585</v>
+        <v>332.4527575170915</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15194,28 +15366,28 @@
         <v>0.0713</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05783699062658833</v>
+        <v>-0.05340894922925666</v>
       </c>
       <c r="J5" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K5" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004180630831628784</v>
+        <v>0.003647966124943003</v>
       </c>
       <c r="M5" t="n">
-        <v>5.20521018143144</v>
+        <v>5.165685399252357</v>
       </c>
       <c r="N5" t="n">
-        <v>41.34337556332977</v>
+        <v>40.91986293870497</v>
       </c>
       <c r="O5" t="n">
-        <v>6.429881457953153</v>
+        <v>6.396863523532839</v>
       </c>
       <c r="P5" t="n">
-        <v>347.308099419517</v>
+        <v>347.2577959210251</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15272,28 +15444,28 @@
         <v>0.055</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05308387187346887</v>
+        <v>-0.06053827943769835</v>
       </c>
       <c r="J6" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K6" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002982999564132394</v>
+        <v>0.003951140360573646</v>
       </c>
       <c r="M6" t="n">
-        <v>5.279755941026555</v>
+        <v>5.247415787942542</v>
       </c>
       <c r="N6" t="n">
-        <v>48.86865265478222</v>
+        <v>48.52465095990768</v>
       </c>
       <c r="O6" t="n">
-        <v>6.990611751111788</v>
+        <v>6.965963749540165</v>
       </c>
       <c r="P6" t="n">
-        <v>344.6816794698632</v>
+        <v>344.7662561753067</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15350,28 +15522,28 @@
         <v>0.0525</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.274918795097123</v>
+        <v>-0.2845561642604873</v>
       </c>
       <c r="J7" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K7" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06039518370083719</v>
+        <v>0.06555754296621841</v>
       </c>
       <c r="M7" t="n">
-        <v>5.995076306113399</v>
+        <v>5.968314785178945</v>
       </c>
       <c r="N7" t="n">
-        <v>61.01092344842698</v>
+        <v>60.6191690074035</v>
       </c>
       <c r="O7" t="n">
-        <v>7.810948946730287</v>
+        <v>7.785831298416599</v>
       </c>
       <c r="P7" t="n">
-        <v>344.322641066842</v>
+        <v>344.43202167994</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15428,28 +15600,28 @@
         <v>0.0557</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2902829388562159</v>
+        <v>-0.2836095924529609</v>
       </c>
       <c r="J8" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K8" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08277935791176616</v>
+        <v>0.08071332234556661</v>
       </c>
       <c r="M8" t="n">
-        <v>5.227431817152175</v>
+        <v>5.215988290944493</v>
       </c>
       <c r="N8" t="n">
-        <v>48.44518249007979</v>
+        <v>48.11623770821833</v>
       </c>
       <c r="O8" t="n">
-        <v>6.960257358034959</v>
+        <v>6.936586891852385</v>
       </c>
       <c r="P8" t="n">
-        <v>350.717956783387</v>
+        <v>350.6420894536527</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -15491,7 +15663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I329"/>
+  <dimension ref="A1:I333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30953,6 +31125,194 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-45.86217011301374,170.74102753095534</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-45.86279013459572,170.74114588104868</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-45.86341075394803,170.7412794780804</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-45.863985935526216,170.7416887255428</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-45.86458743057511,170.7419330903099</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-45.865178746066256,170.74225518681595</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-45.865653410688964,170.74287839180312</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-45.86216862773086,170.7410427072265</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-45.862788262381486,170.74116501101398</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-45.86340482372292,170.74133224329776</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-45.86397915746554,170.74172023365603</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-45.86455845137885,170.7420225929321</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-45.865138315429206,170.74236253989466</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-45.86562037085332,170.74295770019384</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-45.86217045001041,170.74102408759956</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-45.86279055896385,170.74114154492307</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-45.86340992514696,170.74128685249696</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-45.86398744470257,170.74168171006346</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-45.864569536119085,170.74198835760563</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-45.86515116614983,170.74232841818295</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-45.86562990955651,170.7429348036387</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-45.862166593264426,170.74106349489088</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-45.8627853292393,170.7411949812906</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-45.86340992514696,170.74128685249696</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-45.86397709227342,170.7417298337828</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-45.8645567867753,170.74202773407214</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-45.86515116614983,170.74232841818295</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-45.865607560413565,170.74298845014468</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0507/nzd0507.xlsx
+++ b/data/nzd0507/nzd0507.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I333"/>
+  <dimension ref="A1:I335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11412,7 +11412,7 @@
         <v>332.56</v>
       </c>
       <c r="D333" t="n">
-        <v>328.58</v>
+        <v>334.15</v>
       </c>
       <c r="E333" t="n">
         <v>349.67</v>
@@ -11421,12 +11421,78 @@
         <v>343.04</v>
       </c>
       <c r="G333" t="n">
-        <v>333.71</v>
+        <v>338.64</v>
       </c>
       <c r="H333" t="n">
         <v>350.22</v>
       </c>
       <c r="I333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>332.88</v>
+      </c>
+      <c r="C334" t="n">
+        <v>332.09</v>
+      </c>
+      <c r="D334" t="n">
+        <v>332.42</v>
+      </c>
+      <c r="E334" t="n">
+        <v>349.19</v>
+      </c>
+      <c r="F334" t="n">
+        <v>343.18</v>
+      </c>
+      <c r="G334" t="n">
+        <v>337.2</v>
+      </c>
+      <c r="H334" t="n">
+        <v>350.4</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>333.88</v>
+      </c>
+      <c r="C335" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="D335" t="n">
+        <v>334.4</v>
+      </c>
+      <c r="E335" t="n">
+        <v>350.84</v>
+      </c>
+      <c r="F335" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="G335" t="n">
+        <v>339.74</v>
+      </c>
+      <c r="H335" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="I335" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11443,7 +11509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B351"/>
+  <dimension ref="A1:B353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14956,6 +15022,26 @@
       </c>
       <c r="B351" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -15124,28 +15210,28 @@
         <v>0.082</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03096177884438537</v>
+        <v>-0.02964200893588213</v>
       </c>
       <c r="J2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0009148597791395208</v>
+        <v>0.0008486028710730231</v>
       </c>
       <c r="M2" t="n">
-        <v>5.789102900586212</v>
+        <v>5.760767136864588</v>
       </c>
       <c r="N2" t="n">
-        <v>54.28523115537102</v>
+        <v>53.96818874844162</v>
       </c>
       <c r="O2" t="n">
-        <v>7.367851189822648</v>
+        <v>7.346304427972041</v>
       </c>
       <c r="P2" t="n">
-        <v>333.0853332495731</v>
+        <v>333.0701519544188</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15206,28 +15292,28 @@
         <v>0.0743</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05762914648932047</v>
+        <v>-0.05771433908416274</v>
       </c>
       <c r="J3" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K3" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002955059072883737</v>
+        <v>0.002999247971908314</v>
       </c>
       <c r="M3" t="n">
-        <v>6.229548146277886</v>
+        <v>6.195818337586817</v>
       </c>
       <c r="N3" t="n">
-        <v>58.85414167212879</v>
+        <v>58.50391173031802</v>
       </c>
       <c r="O3" t="n">
-        <v>7.671645304113635</v>
+        <v>7.648784983925095</v>
       </c>
       <c r="P3" t="n">
-        <v>334.3039343274995</v>
+        <v>334.3049025397224</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15288,28 +15374,28 @@
         <v>0.0709</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0177711643382485</v>
+        <v>-0.01291264048173052</v>
       </c>
       <c r="J4" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K4" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002275419185215899</v>
+        <v>0.0001215986864901986</v>
       </c>
       <c r="M4" t="n">
-        <v>6.81553772365961</v>
+        <v>6.779231353702874</v>
       </c>
       <c r="N4" t="n">
-        <v>72.88121550439151</v>
+        <v>72.44072063479099</v>
       </c>
       <c r="O4" t="n">
-        <v>8.537049578419438</v>
+        <v>8.511211466929428</v>
       </c>
       <c r="P4" t="n">
-        <v>332.4527575170915</v>
+        <v>332.3974395173944</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15366,28 +15452,28 @@
         <v>0.0713</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05340894922925666</v>
+        <v>-0.04855717834490456</v>
       </c>
       <c r="J5" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K5" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003647966124943003</v>
+        <v>0.003045413778076322</v>
       </c>
       <c r="M5" t="n">
-        <v>5.165685399252357</v>
+        <v>5.159776167499059</v>
       </c>
       <c r="N5" t="n">
-        <v>40.91986293870497</v>
+        <v>40.78216627394484</v>
       </c>
       <c r="O5" t="n">
-        <v>6.396863523532839</v>
+        <v>6.386091627431041</v>
       </c>
       <c r="P5" t="n">
-        <v>347.2577959210251</v>
+        <v>347.2024308842167</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15444,28 +15530,28 @@
         <v>0.055</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06053827943769835</v>
+        <v>-0.05949408901079498</v>
       </c>
       <c r="J6" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K6" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003951140360573646</v>
+        <v>0.003861571942382458</v>
       </c>
       <c r="M6" t="n">
-        <v>5.247415787942542</v>
+        <v>5.222277194865524</v>
       </c>
       <c r="N6" t="n">
-        <v>48.52465095990768</v>
+        <v>48.24335932727722</v>
       </c>
       <c r="O6" t="n">
-        <v>6.965963749540165</v>
+        <v>6.945743972194571</v>
       </c>
       <c r="P6" t="n">
-        <v>344.7662561753067</v>
+        <v>344.754336176848</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15522,28 +15608,28 @@
         <v>0.0525</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2845561642604873</v>
+        <v>-0.2798018808327709</v>
       </c>
       <c r="J7" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K7" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06555754296621841</v>
+        <v>0.06423388784585216</v>
       </c>
       <c r="M7" t="n">
-        <v>5.968314785178945</v>
+        <v>5.939843441935661</v>
       </c>
       <c r="N7" t="n">
-        <v>60.6191690074035</v>
+        <v>60.26132870544958</v>
       </c>
       <c r="O7" t="n">
-        <v>7.785831298416599</v>
+        <v>7.762817059898396</v>
       </c>
       <c r="P7" t="n">
-        <v>344.43202167994</v>
+        <v>344.3778768467749</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15600,28 +15686,28 @@
         <v>0.0557</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2836095924529609</v>
+        <v>-0.2746791063899015</v>
       </c>
       <c r="J8" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K8" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08071332234556661</v>
+        <v>0.07641956265213457</v>
       </c>
       <c r="M8" t="n">
-        <v>5.215988290944493</v>
+        <v>5.231233261320979</v>
       </c>
       <c r="N8" t="n">
-        <v>48.11623770821833</v>
+        <v>48.17877672402707</v>
       </c>
       <c r="O8" t="n">
-        <v>6.936586891852385</v>
+        <v>6.941093337798237</v>
       </c>
       <c r="P8" t="n">
-        <v>350.6420894536527</v>
+        <v>350.5401884251374</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -15663,7 +15749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I333"/>
+  <dimension ref="A1:I335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31284,7 +31370,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>-45.86340992514696,170.74128685249696</t>
+          <t>-45.86340196577431,170.7413576723145</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -31299,7 +31385,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>-45.86515116614983,170.74232841818295</t>
+          <t>-45.865130118286274,170.7423843052309</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -31308,6 +31394,100 @@
         </is>
       </c>
       <c r="I333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>-45.862167217334296,170.74105711830688</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>-45.86278591586838,170.7411889872355</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>-45.863404437900186,170.7413356762152</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-45.86397836316099,170.74172392601255</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-45.86455625712867,170.74202936988934</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-45.865136266143864,170.7423679812293</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-45.86560673096035,170.74299044114824</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-45.862165969194216,170.7410698714748</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>-45.862784418091394,170.74120429120572</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>-45.86340160853034,170.74136085094142</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-45.863973994483715,170.74174423397167</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-45.86454971220761,170.74204958391388</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-45.86512542200456,170.74239677495194</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-45.86560345922782,170.74299829455046</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
